--- a/Cronograma de Tareas/Cronograma Septiembre.xlsx
+++ b/Cronograma de Tareas/Cronograma Septiembre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel Puentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDCF34D-0D6D-4B5C-B30A-EF6C11BDC859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3059B9C1-9983-499D-BC6B-2A8F3BF9664D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 31 Ago al 6 Sep" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="84">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -525,397 +525,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="76">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="38">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2321,38 +1941,38 @@
       </c>
     </row>
     <row r="31" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="1"/>
-    </row>
-    <row r="32" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="13" t="s">
-        <v>81</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D32"/>
       <c r="F32" s="1"/>
-      <c r="H32" s="20" t="s">
+      <c r="H32" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="I32" s="19"/>
+      <c r="I32" s="20"/>
       <c r="K32" s="18" t="s">
         <v>48</v>
       </c>
       <c r="L32" s="18"/>
     </row>
     <row r="33" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="6" t="s">
-        <v>45</v>
+      <c r="B33" s="13" t="s">
+        <v>81</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="D33"/>
       <c r="F33" s="1"/>
@@ -2370,7 +1990,12 @@
       </c>
     </row>
     <row r="34" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="1"/>
+      <c r="B34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="D34"/>
       <c r="F34" s="1"/>
       <c r="H34" s="6" t="s">
@@ -2471,17 +2096,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="H18:I18"/>
     <mergeCell ref="K18:L18"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="H32:I32"/>
     <mergeCell ref="K32:L32"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:F17"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="37" priority="35"/>
@@ -2501,10 +2126,10 @@
   <conditionalFormatting sqref="B29 B10">
     <cfRule type="duplicateValues" dxfId="32" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30 B9">
+  <conditionalFormatting sqref="B9 B30:B31">
     <cfRule type="duplicateValues" dxfId="31" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31 B26 B11">
+  <conditionalFormatting sqref="B32 B26 B11">
     <cfRule type="duplicateValues" dxfId="30" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
@@ -2817,12 +2442,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -3023,6 +2642,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3033,15 +2658,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3060,6 +2676,15 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
   <ds:schemaRefs>

--- a/Cronograma de Tareas/Cronograma Septiembre.xlsx
+++ b/Cronograma de Tareas/Cronograma Septiembre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel Puentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3059B9C1-9983-499D-BC6B-2A8F3BF9664D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7F691D-4460-4972-8D78-1C1BEE8C04E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="83">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -311,9 +311,6 @@
   </si>
   <si>
     <t>Revisión Calendarios</t>
-  </si>
-  <si>
-    <t>Alejandra / Sebastian Hincapie</t>
   </si>
   <si>
     <t>Inactivaciones Usuarios - Contracargos (Correo)</t>
@@ -1760,7 +1757,7 @@
         <v>34</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>14</v>
@@ -1923,7 +1920,7 @@
         <v>43</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1"/>
       <c r="H30" s="8" t="s">

--- a/Cronograma de Tareas/Cronograma Septiembre.xlsx
+++ b/Cronograma de Tareas/Cronograma Septiembre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel Puentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7F691D-4460-4972-8D78-1C1BEE8C04E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6EA6F0-4021-4D3B-86B2-160CD114DB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 31 Ago al 6 Sep" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="82">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -70,9 +70,6 @@
   </si>
   <si>
     <t>Revision de Billetera Usuarios - PDV (Desfase)</t>
-  </si>
-  <si>
-    <t>Luis</t>
   </si>
   <si>
     <t>Aprobación de retiros Punto de Venta</t>
@@ -1244,24 +1241,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CAF266D-0085-4B50-B3FE-269B78B845C1}">
   <dimension ref="A2:L41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="15" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="56.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.5703125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.453125" customWidth="1"/>
+    <col min="2" max="2" width="56.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.453125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.54296875" style="2" customWidth="1"/>
     <col min="8" max="8" width="55" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.42578125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.453125" style="2" customWidth="1"/>
     <col min="11" max="11" width="55" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.26953125" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="15" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B2" s="18" t="s">
         <v>0</v>
       </c>
@@ -1280,7 +1277,7 @@
       </c>
       <c r="L2" s="18"/>
     </row>
-    <row r="3" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1307,288 +1304,288 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>41</v>
-      </c>
       <c r="K5" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="6" t="s">
+      <c r="I6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>41</v>
-      </c>
       <c r="K7" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B8" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>7</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B9" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>41</v>
-      </c>
       <c r="K9" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B10" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L10" s="7" t="s">
+      <c r="F11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="5" t="s">
+      <c r="I11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>41</v>
-      </c>
       <c r="K11" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B12" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>18</v>
-      </c>
       <c r="I12" s="7" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>41</v>
-      </c>
       <c r="K13" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B14" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="1"/>
       <c r="E14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="I14" s="7" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1596,93 +1593,93 @@
         <v>5</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>41</v>
-      </c>
       <c r="K15" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B16" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F16"/>
       <c r="G16" s="1"/>
       <c r="H16" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B17" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F17" s="18"/>
     </row>
-    <row r="18" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B18" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I18" s="18"/>
       <c r="K18" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L18" s="18"/>
     </row>
-    <row r="19" spans="2:12" s="2" customFormat="1" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" s="2" customFormat="1" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>14</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>6</v>
@@ -1697,120 +1694,120 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B20" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="B21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="12" t="s">
+      <c r="C22" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I20" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K20" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B21" s="8" t="s">
+      <c r="H22" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K21" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>7</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C23" s="1"/>
       <c r="F23" s="1"/>
       <c r="H23" s="12" t="s">
         <v>7</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B24" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" s="18"/>
       <c r="F24" s="1"/>
       <c r="H24" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
@@ -1819,136 +1816,136 @@
       </c>
       <c r="F25" s="1"/>
       <c r="H25" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B26" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F26" s="1"/>
       <c r="H26" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="B27" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F27" s="1"/>
       <c r="H27" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B28" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F28" s="1"/>
       <c r="H28" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B29" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F29" s="1"/>
       <c r="H29" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B30" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F30" s="1"/>
       <c r="H30" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J30" s="1"/>
       <c r="K30" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B31" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B32" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>8</v>
@@ -1956,17 +1953,17 @@
       <c r="D32"/>
       <c r="F32" s="1"/>
       <c r="H32" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I32" s="20"/>
       <c r="K32" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L32" s="18"/>
     </row>
-    <row r="33" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B33" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>8</v>
@@ -1974,136 +1971,136 @@
       <c r="D33"/>
       <c r="F33" s="1"/>
       <c r="H33" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="D34"/>
       <c r="F34" s="1"/>
       <c r="H34" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I34" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I34" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="K34" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L34" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C35" s="1"/>
       <c r="D35"/>
       <c r="F35" s="1"/>
       <c r="H35" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C36" s="1"/>
       <c r="D36"/>
       <c r="F36" s="1"/>
       <c r="H36" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L36" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C37" s="1"/>
       <c r="D37"/>
       <c r="F37" s="1"/>
       <c r="H37" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L37" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C38" s="1"/>
       <c r="D38"/>
       <c r="F38" s="1"/>
       <c r="H38" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C39" s="1"/>
       <c r="D39"/>
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C40" s="1"/>
       <c r="D40"/>
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C41" s="1"/>
       <c r="D41"/>
       <c r="F41" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="K32:L32"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="37" priority="35"/>
@@ -2114,17 +2111,17 @@
   <conditionalFormatting sqref="B8">
     <cfRule type="duplicateValues" dxfId="35" priority="32"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B9 B30:B31">
+    <cfRule type="duplicateValues" dxfId="34" priority="37"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="34" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22 B28">
-    <cfRule type="duplicateValues" dxfId="33" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B10">
-    <cfRule type="duplicateValues" dxfId="32" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9 B30:B31">
-    <cfRule type="duplicateValues" dxfId="31" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B26 B11">
     <cfRule type="duplicateValues" dxfId="30" priority="38"/>
@@ -2226,210 +2223,210 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09747FE2-332F-458B-9A08-92605154E49F}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="95.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="95.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="94.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="94.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="14" t="s">
+    </row>
+    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="8" t="s">
+    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B6" s="8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="8" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+    <row r="8" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="B11" s="8" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="8" t="s">
+    <row r="12" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="15" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="B12" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="8" t="s">
+    </row>
+    <row r="13" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="145" x14ac:dyDescent="0.35">
+      <c r="A20" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="135" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="105" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+      <c r="B20" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="150" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="8" t="s">
+      <c r="B22" s="8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="8" t="s">
+    <row r="23" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="105" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="8" t="s">
+    <row r="24" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A24" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="8" t="s">
+    <row r="25" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2439,6 +2436,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -2639,12 +2642,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2655,6 +2652,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2673,15 +2679,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
   <ds:schemaRefs>

--- a/Cronograma de Tareas/Cronograma Septiembre.xlsx
+++ b/Cronograma de Tareas/Cronograma Septiembre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel Puentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6EA6F0-4021-4D3B-86B2-160CD114DB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8EEBD9-DEEA-40BB-B0D1-398B61BB4D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="85">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -311,6 +311,15 @@
   </si>
   <si>
     <t>Inactivaciones Usuarios - Contracargos (Correo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Jose </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriana </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel </t>
   </si>
 </sst>
 </file>
@@ -1347,7 +1356,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>12</v>
@@ -1399,7 +1408,7 @@
         <v>18</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>18</v>
@@ -1451,7 +1460,7 @@
         <v>10</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>10</v>
@@ -1503,7 +1512,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>15</v>
@@ -1551,7 +1560,7 @@
         <v>20</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>20</v>
@@ -1602,7 +1611,7 @@
         <v>21</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="K15" s="10" t="s">
         <v>21</v>
@@ -1717,7 +1726,7 @@
         <v>12</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="2:12" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
@@ -1743,7 +1752,7 @@
         <v>16</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
@@ -1769,7 +1778,7 @@
         <v>7</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
@@ -1785,7 +1794,7 @@
         <v>10</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
@@ -1804,7 +1813,7 @@
         <v>23</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
@@ -1825,7 +1834,7 @@
         <v>15</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
@@ -1846,7 +1855,7 @@
         <v>17</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="2:12" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
@@ -1867,7 +1876,7 @@
         <v>20</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
@@ -1888,7 +1897,7 @@
         <v>22</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
@@ -1909,7 +1918,7 @@
         <v>21</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
@@ -1931,7 +1940,7 @@
         <v>79</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
@@ -2002,7 +2011,7 @@
         <v>12</v>
       </c>
       <c r="L34" s="5" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
@@ -2019,7 +2028,7 @@
         <v>16</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
@@ -2036,7 +2045,7 @@
         <v>43</v>
       </c>
       <c r="L36" s="5" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
@@ -2053,7 +2062,7 @@
         <v>22</v>
       </c>
       <c r="L37" s="5" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
@@ -2070,7 +2079,7 @@
         <v>21</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
@@ -2090,17 +2099,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="K32:L32"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="37" priority="35"/>
@@ -2436,9 +2445,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2643,19 +2655,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2680,9 +2688,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Septiembre.xlsx
+++ b/Cronograma de Tareas/Cronograma Septiembre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel Puentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8EEBD9-DEEA-40BB-B0D1-398B61BB4D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57794C45-752E-4FDF-AC5E-D97B6C9D347A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 31 Ago al 6 Sep" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="86">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t xml:space="preserve">Daniel </t>
+  </si>
+  <si>
+    <t>Apoyo Deltas (Registros, Bonos, Premios Bonos y Bonos Casino)</t>
   </si>
 </sst>
 </file>
@@ -476,7 +479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -524,6 +527,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1268,23 +1274,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="18"/>
+      <c r="C2" s="19"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="18"/>
-      <c r="H2" s="18" t="s">
+      <c r="F2" s="19"/>
+      <c r="H2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="18"/>
-      <c r="K2" s="18" t="s">
+      <c r="I2" s="19"/>
+      <c r="K2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="18"/>
+      <c r="L2" s="19"/>
     </row>
     <row r="3" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
@@ -1548,7 +1554,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="1"/>
+      <c r="B13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="D13" s="1"/>
       <c r="E13" s="6" t="s">
         <v>22</v>
@@ -1570,10 +1581,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="18"/>
+      <c r="B14" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="D14" s="1"/>
       <c r="E14" s="6" t="s">
         <v>21</v>
@@ -1595,12 +1608,6 @@
       </c>
     </row>
     <row r="15" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="E15" s="6" t="s">
         <v>36</v>
       </c>
@@ -1621,12 +1628,6 @@
       </c>
     </row>
     <row r="16" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="F16"/>
       <c r="G16" s="1"/>
       <c r="H16" s="8" t="s">
@@ -1644,23 +1645,21 @@
       </c>
     </row>
     <row r="17" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="18" t="s">
+      <c r="B17" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="E17" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="18"/>
+      <c r="F17" s="19"/>
     </row>
     <row r="18" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>33</v>
+      <c r="B18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>39</v>
@@ -1668,18 +1667,18 @@
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H18" s="18" t="s">
+      <c r="H18" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="18"/>
-      <c r="K18" s="18" t="s">
+      <c r="I18" s="19"/>
+      <c r="K18" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="18"/>
+      <c r="L18" s="19"/>
     </row>
     <row r="19" spans="2:12" s="2" customFormat="1" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="6" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>33</v>
@@ -1704,8 +1703,8 @@
       </c>
     </row>
     <row r="20" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="8" t="s">
-        <v>18</v>
+      <c r="B20" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>33</v>
@@ -1729,9 +1728,9 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="2:12" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B21" s="8" t="s">
-        <v>31</v>
+    <row r="21" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>33</v>
@@ -1756,8 +1755,8 @@
       </c>
     </row>
     <row r="22" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="8" t="s">
-        <v>34</v>
+      <c r="B22" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>33</v>
@@ -1782,7 +1781,12 @@
       </c>
     </row>
     <row r="23" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="1"/>
+      <c r="B23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="F23" s="1"/>
       <c r="H23" s="12" t="s">
         <v>7</v>
@@ -1797,11 +1801,13 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="18"/>
+    <row r="24" spans="2:12" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="B24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="F24" s="1"/>
       <c r="H24" s="12" t="s">
         <v>20</v>
@@ -1817,11 +1823,11 @@
       </c>
     </row>
     <row r="25" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>5</v>
+      <c r="B25" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="F25" s="1"/>
       <c r="H25" s="12" t="s">
@@ -1838,12 +1844,7 @@
       </c>
     </row>
     <row r="26" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="C26" s="1"/>
       <c r="F26" s="1"/>
       <c r="H26" s="12" t="s">
         <v>17</v>
@@ -1858,13 +1859,11 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="2:12" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B27" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>14</v>
-      </c>
+    <row r="27" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="18"/>
       <c r="F27" s="1"/>
       <c r="H27" s="12" t="s">
         <v>23</v>
@@ -1880,11 +1879,11 @@
       </c>
     </row>
     <row r="28" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>14</v>
+      <c r="B28" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F28" s="1"/>
       <c r="H28" s="12" t="s">
@@ -1901,8 +1900,8 @@
       </c>
     </row>
     <row r="29" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="6" t="s">
-        <v>22</v>
+      <c r="B29" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>14</v>
@@ -1921,12 +1920,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="6" t="s">
-        <v>42</v>
+    <row r="30" spans="2:12" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="B30" s="17" t="s">
+        <v>35</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F30" s="1"/>
       <c r="H30" s="8" t="s">
@@ -1944,8 +1943,8 @@
       </c>
     </row>
     <row r="31" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="6" t="s">
-        <v>42</v>
+      <c r="B31" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>14</v>
@@ -1953,26 +1952,26 @@
       <c r="F31" s="1"/>
     </row>
     <row r="32" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="8" t="s">
-        <v>41</v>
+      <c r="B32" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D32"/>
       <c r="F32" s="1"/>
-      <c r="H32" s="19" t="s">
+      <c r="H32" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="20"/>
-      <c r="K32" s="18" t="s">
+      <c r="I32" s="21"/>
+      <c r="K32" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="18"/>
+      <c r="L32" s="19"/>
     </row>
     <row r="33" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="13" t="s">
-        <v>80</v>
+      <c r="B33" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>8</v>
@@ -1994,10 +1993,10 @@
     </row>
     <row r="34" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B34" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D34"/>
       <c r="F34" s="1"/>
@@ -2015,7 +2014,12 @@
       </c>
     </row>
     <row r="35" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C35" s="1"/>
+      <c r="B35" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D35"/>
       <c r="F35" s="1"/>
       <c r="H35" s="6" t="s">
@@ -2032,7 +2036,12 @@
       </c>
     </row>
     <row r="36" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C36" s="1"/>
+      <c r="B36" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D36"/>
       <c r="F36" s="1"/>
       <c r="H36" s="6" t="s">
@@ -2049,7 +2058,12 @@
       </c>
     </row>
     <row r="37" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="1"/>
+      <c r="B37" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="D37"/>
       <c r="F37" s="1"/>
       <c r="H37" s="6" t="s">
@@ -2098,18 +2112,17 @@
       <c r="F41" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="37" priority="35"/>
@@ -2120,19 +2133,19 @@
   <conditionalFormatting sqref="B8">
     <cfRule type="duplicateValues" dxfId="35" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B9 B30:B31">
+  <conditionalFormatting sqref="B33:B34 B9">
     <cfRule type="duplicateValues" dxfId="34" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
     <cfRule type="duplicateValues" dxfId="33" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B22 B28">
+  <conditionalFormatting sqref="B25 B31">
     <cfRule type="duplicateValues" dxfId="32" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29 B10">
+  <conditionalFormatting sqref="B32 B10">
     <cfRule type="duplicateValues" dxfId="31" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B32 B26 B11">
+  <conditionalFormatting sqref="B35 B29 B11">
     <cfRule type="duplicateValues" dxfId="30" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
@@ -2454,6 +2467,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -2654,12 +2673,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
   <ds:schemaRefs>
@@ -2669,6 +2682,15 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2685,13 +2707,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Septiembre.xlsx
+++ b/Cronograma de Tareas/Cronograma Septiembre.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel Puentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57794C45-752E-4FDF-AC5E-D97B6C9D347A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D110E4-3839-45A6-A40F-B4A2F9BC0A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 31 Ago al 6 Sep" sheetId="8" r:id="rId1"/>
-    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId2"/>
+    <sheet name="Semana 2 - 7 Sep al 13 Sep" sheetId="9" r:id="rId2"/>
+    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="102">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -323,6 +324,54 @@
   </si>
   <si>
     <t>Apoyo Deltas (Registros, Bonos, Premios Bonos y Bonos Casino)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alexander </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alejandra </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yefferson </t>
+  </si>
+  <si>
+    <t>Revisión GGR negativo casino / deportivo desde las 11:00 am</t>
+  </si>
+  <si>
+    <t>Revisión de Registros desde las 11:00 am</t>
+  </si>
+  <si>
+    <t>Aprobación de retiros Punto de Venta desde las 11:00 am</t>
+  </si>
+  <si>
+    <t>Respuesta WhatsApp desde las 11:00 am</t>
+  </si>
+  <si>
+    <t>Solución Casos Jira desde las 11:00 am</t>
+  </si>
+  <si>
+    <t>Respuesta Contracargos (Correo) desde las 11:00 am</t>
+  </si>
+  <si>
+    <t>Set 1 Noche</t>
+  </si>
+  <si>
+    <t>Revisión GGR negativo casino / deportivo desde las 6:00 pm</t>
+  </si>
+  <si>
+    <t>Aprobación de retiros Punto de Venta desde las 6:00 Pm</t>
+  </si>
+  <si>
+    <t>Respuesta WhatsApp desde las 6:00 pm</t>
+  </si>
+  <si>
+    <t>Respuesta Contracargos (Correo) desde las 6:00 pm</t>
+  </si>
+  <si>
+    <t>Alejandra / Sebastian Hincapie</t>
+  </si>
+  <si>
+    <t>Apoyo Revisión GGR negativo casino / deportivo</t>
   </si>
 </sst>
 </file>
@@ -479,7 +528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -540,11 +589,313 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="38">
+  <dxfs count="67">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2113,136 +2464,1247 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="H18:I18"/>
     <mergeCell ref="K18:L18"/>
     <mergeCell ref="H32:I32"/>
     <mergeCell ref="K32:L32"/>
     <mergeCell ref="E17:F17"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="66" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="duplicateValues" dxfId="65" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="duplicateValues" dxfId="64" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="duplicateValues" dxfId="63" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25 B31">
+    <cfRule type="duplicateValues" dxfId="62" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32 B10">
+    <cfRule type="duplicateValues" dxfId="61" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33:B34 B9">
+    <cfRule type="duplicateValues" dxfId="60" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35 B29 B11">
+    <cfRule type="duplicateValues" dxfId="59" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="duplicateValues" dxfId="58" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="duplicateValues" dxfId="57" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="duplicateValues" dxfId="56" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="duplicateValues" dxfId="55" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="duplicateValues" dxfId="54" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="duplicateValues" dxfId="53" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="duplicateValues" dxfId="52" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E15">
+    <cfRule type="duplicateValues" dxfId="51" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E22">
+    <cfRule type="duplicateValues" dxfId="50" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="duplicateValues" dxfId="49" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="duplicateValues" dxfId="48" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="duplicateValues" dxfId="47" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="duplicateValues" dxfId="46" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="duplicateValues" dxfId="45" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24">
+    <cfRule type="duplicateValues" dxfId="44" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25:H26">
+    <cfRule type="duplicateValues" dxfId="43" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30">
+    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H37">
+    <cfRule type="duplicateValues" dxfId="41" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H38">
+    <cfRule type="duplicateValues" dxfId="40" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4">
+    <cfRule type="duplicateValues" dxfId="39" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K11">
+    <cfRule type="duplicateValues" dxfId="38" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12">
+    <cfRule type="duplicateValues" dxfId="37" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13">
+    <cfRule type="duplicateValues" dxfId="36" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K16">
+    <cfRule type="duplicateValues" dxfId="35" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K25">
+    <cfRule type="duplicateValues" dxfId="34" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K26">
+    <cfRule type="duplicateValues" dxfId="33" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K27">
+    <cfRule type="duplicateValues" dxfId="32" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K30">
+    <cfRule type="duplicateValues" dxfId="31" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K37">
+    <cfRule type="duplicateValues" dxfId="30" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K38">
+    <cfRule type="duplicateValues" dxfId="29" priority="23"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4492F1BB-C491-4DF0-AED4-7076F62446D0}">
+  <dimension ref="A1:L38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2.453125" customWidth="1"/>
+    <col min="2" max="2" width="87.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="47.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="49.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+      <c r="B2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="19"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="19"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="19"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="B11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="J13" s="2"/>
+      <c r="K13" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+      <c r="B14" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="J15" s="2"/>
+      <c r="K15" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+      <c r="B17" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F18" s="19"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="19"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="L18" s="19"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+      <c r="B20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="2"/>
+      <c r="K20" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
+      <c r="B21" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J21" s="2"/>
+      <c r="K21" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A22" s="2"/>
+      <c r="B22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="2"/>
+      <c r="K22" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A23" s="2"/>
+      <c r="B23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="2"/>
+      <c r="B24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="2"/>
+      <c r="K24" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A25" s="2"/>
+      <c r="B25" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J25" s="2"/>
+      <c r="K25" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="2"/>
+      <c r="K26" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A27" s="2"/>
+      <c r="B27" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J27" s="2"/>
+      <c r="K27" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" s="2"/>
+      <c r="K28" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29" s="2"/>
+      <c r="B29" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J29" s="2"/>
+      <c r="K29" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="2"/>
+      <c r="B30" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J30" s="1"/>
+      <c r="K30" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A31" s="2"/>
+      <c r="B31" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+      <c r="B32" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="I32" s="21"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="L32" s="19"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+      <c r="B33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="2"/>
+      <c r="K33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A34" s="2"/>
+      <c r="B34" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J34" s="2"/>
+      <c r="K34" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A35" s="2"/>
+      <c r="B35" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J35" s="2"/>
+      <c r="K35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="1"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J36" s="2"/>
+      <c r="K36" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="1"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J37" s="2"/>
+      <c r="K37" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="1"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J38" s="2"/>
+      <c r="K38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="B17:C17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="37" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="36" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="35" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B33:B34 B9">
-    <cfRule type="duplicateValues" dxfId="34" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="33" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12 B15">
+    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25 B31">
-    <cfRule type="duplicateValues" dxfId="32" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="31" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35 B29 B11">
-    <cfRule type="duplicateValues" dxfId="30" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33 B9">
+    <cfRule type="duplicateValues" dxfId="22" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34 B29 B11">
+    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="29" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="27" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="26" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="25" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="24" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="23" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="22" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E22">
-    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="17" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H24">
-    <cfRule type="duplicateValues" dxfId="15" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H25:H26">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H30">
-    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E23">
+    <cfRule type="duplicateValues" dxfId="12" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37">
-    <cfRule type="duplicateValues" dxfId="12" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38">
-    <cfRule type="duplicateValues" dxfId="11" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="9" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="8" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="6" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K27">
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K24">
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K25:K26">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30">
-    <cfRule type="duplicateValues" dxfId="2" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37">
-    <cfRule type="duplicateValues" dxfId="1" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09747FE2-332F-458B-9A08-92605154E49F}">
   <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="95.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2458,21 +3920,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -2673,24 +4120,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2707,4 +4152,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Septiembre.xlsx
+++ b/Cronograma de Tareas/Cronograma Septiembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel Puentes\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/luis_fuentes_virtualsoft_tech/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D110E4-3839-45A6-A40F-B4A2F9BC0A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{916904B6-0074-4A61-814B-CAA1D2DFFDAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 31 Ago al 6 Sep" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="101">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -366,9 +366,6 @@
   </si>
   <si>
     <t>Respuesta Contracargos (Correo) desde las 6:00 pm</t>
-  </si>
-  <si>
-    <t>Alejandra / Sebastian Hincapie</t>
   </si>
   <si>
     <t>Apoyo Revisión GGR negativo casino / deportivo</t>
@@ -580,15 +577,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -600,6 +588,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1607,43 +1604,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CAF266D-0085-4B50-B3FE-269B78B845C1}">
   <dimension ref="A2:L41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="15" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.453125" customWidth="1"/>
-    <col min="2" max="2" width="56.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.453125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.54296875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" customWidth="1"/>
+    <col min="2" max="2" width="56.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5546875" style="2" customWidth="1"/>
     <col min="8" max="8" width="55" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.453125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.44140625" style="2" customWidth="1"/>
     <col min="11" max="11" width="55" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="15" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="19" t="s">
+    <row r="2" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="19"/>
+      <c r="C2" s="23"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="19"/>
-      <c r="H2" s="19" t="s">
+      <c r="F2" s="23"/>
+      <c r="H2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="19"/>
-      <c r="K2" s="19" t="s">
+      <c r="I2" s="23"/>
+      <c r="K2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="19"/>
-    </row>
-    <row r="3" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="L2" s="23"/>
+    </row>
+    <row r="3" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1670,7 +1667,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1696,7 +1693,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -1722,7 +1719,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -1748,7 +1745,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -1774,7 +1771,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -1800,7 +1797,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -1826,7 +1823,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -1852,7 +1849,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>30</v>
       </c>
@@ -1878,7 +1875,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>36</v>
       </c>
@@ -1904,7 +1901,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>12</v>
       </c>
@@ -1931,7 +1928,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
         <v>85</v>
       </c>
@@ -1958,7 +1955,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E15" s="6" t="s">
         <v>36</v>
       </c>
@@ -1978,7 +1975,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="F16"/>
       <c r="G16" s="1"/>
       <c r="H16" s="8" t="s">
@@ -1995,17 +1992,17 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="19" t="s">
+    <row r="17" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="E17" s="19" t="s">
+      <c r="C17" s="23"/>
+      <c r="E17" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="19"/>
-    </row>
-    <row r="18" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F17" s="23"/>
+    </row>
+    <row r="18" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>4</v>
       </c>
@@ -2018,16 +2015,16 @@
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H18" s="19" t="s">
+      <c r="H18" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="19"/>
-      <c r="K18" s="19" t="s">
+      <c r="I18" s="23"/>
+      <c r="K18" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="19"/>
-    </row>
-    <row r="19" spans="2:12" s="2" customFormat="1" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L18" s="23"/>
+    </row>
+    <row r="19" spans="2:12" s="2" customFormat="1" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
         <v>12</v>
       </c>
@@ -2053,7 +2050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
         <v>16</v>
       </c>
@@ -2079,7 +2076,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>23</v>
       </c>
@@ -2105,7 +2102,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
         <v>26</v>
       </c>
@@ -2131,7 +2128,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>18</v>
       </c>
@@ -2152,7 +2149,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="2:12" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B24" s="8" t="s">
         <v>31</v>
       </c>
@@ -2173,7 +2170,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B25" s="8" t="s">
         <v>34</v>
       </c>
@@ -2194,7 +2191,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C26" s="1"/>
       <c r="F26" s="1"/>
       <c r="H26" s="12" t="s">
@@ -2210,7 +2207,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B27" s="18" t="s">
         <v>38</v>
       </c>
@@ -2229,7 +2226,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>4</v>
       </c>
@@ -2250,7 +2247,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="s">
         <v>27</v>
       </c>
@@ -2271,7 +2268,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="2:12" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B30" s="17" t="s">
         <v>35</v>
       </c>
@@ -2293,7 +2290,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
         <v>79</v>
       </c>
@@ -2302,7 +2299,7 @@
       </c>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
         <v>22</v>
       </c>
@@ -2311,16 +2308,16 @@
       </c>
       <c r="D32"/>
       <c r="F32" s="1"/>
-      <c r="H32" s="20" t="s">
+      <c r="H32" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="21"/>
-      <c r="K32" s="19" t="s">
+      <c r="I32" s="25"/>
+      <c r="K32" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="19"/>
-    </row>
-    <row r="33" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="L32" s="23"/>
+    </row>
+    <row r="33" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
         <v>42</v>
       </c>
@@ -2342,7 +2339,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B34" s="6" t="s">
         <v>42</v>
       </c>
@@ -2364,7 +2361,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B35" s="8" t="s">
         <v>41</v>
       </c>
@@ -2386,7 +2383,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B36" s="13" t="s">
         <v>80</v>
       </c>
@@ -2408,7 +2405,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
         <v>44</v>
       </c>
@@ -2430,7 +2427,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C38" s="1"/>
       <c r="D38"/>
       <c r="F38" s="1"/>
@@ -2447,33 +2444,33 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C39" s="1"/>
       <c r="D39"/>
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C40" s="1"/>
       <c r="D40"/>
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C41" s="1"/>
       <c r="D41"/>
       <c r="F41" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="E17:F17"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="E17:F17"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="66" priority="35"/>
@@ -2596,20 +2593,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4492F1BB-C491-4DF0-AED4-7076F62446D0}">
   <dimension ref="A1:L38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.453125" customWidth="1"/>
-    <col min="2" max="2" width="87.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="47.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="49.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.44140625" customWidth="1"/>
+    <col min="2" max="2" width="87.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="47.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="49.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="1"/>
@@ -2623,29 +2620,29 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="19"/>
+      <c r="C2" s="23"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="19"/>
+      <c r="F2" s="23"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="19"/>
+      <c r="I2" s="23"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="19"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L2" s="23"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="3" t="s">
         <v>4</v>
@@ -2675,7 +2672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="4" t="s">
         <v>7</v>
@@ -2705,7 +2702,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -2735,7 +2732,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="6" t="s">
         <v>9</v>
@@ -2765,7 +2762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="6" t="s">
         <v>15</v>
@@ -2781,7 +2778,7 @@
         <v>32</v>
       </c>
       <c r="G7" s="2"/>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="19" t="s">
         <v>18</v>
       </c>
       <c r="I7" s="7" t="s">
@@ -2795,7 +2792,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="6" t="s">
         <v>17</v>
@@ -2811,7 +2808,7 @@
         <v>86</v>
       </c>
       <c r="G8" s="2"/>
-      <c r="H8" s="23" t="s">
+      <c r="H8" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I8" s="5" t="s">
@@ -2825,7 +2822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="6" t="s">
         <v>20</v>
@@ -2855,7 +2852,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="6" t="s">
         <v>21</v>
@@ -2885,7 +2882,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="8" t="s">
         <v>30</v>
@@ -2915,7 +2912,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="6" t="s">
         <v>36</v>
@@ -2945,10 +2942,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>88</v>
@@ -2975,7 +2972,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="6" t="s">
         <v>85</v>
@@ -3005,7 +3002,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="1"/>
@@ -3031,7 +3028,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="1"/>
@@ -3043,7 +3040,7 @@
         <v>45</v>
       </c>
       <c r="G16" s="1"/>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="19" t="s">
         <v>79</v>
       </c>
       <c r="I16" s="5" t="s">
@@ -3057,12 +3054,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="19"/>
+      <c r="C17" s="23"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="G17" s="2"/>
@@ -3072,7 +3069,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="3" t="s">
         <v>4</v>
@@ -3081,22 +3078,22 @@
         <v>5</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="F18" s="19"/>
+      <c r="F18" s="23"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="19" t="s">
+      <c r="H18" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="19"/>
+      <c r="I18" s="23"/>
       <c r="J18" s="2"/>
-      <c r="K18" s="19" t="s">
+      <c r="K18" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="19"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L18" s="23"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="6" t="s">
         <v>12</v>
@@ -3126,7 +3123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="6" t="s">
         <v>16</v>
@@ -3156,7 +3153,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="6" t="s">
         <v>23</v>
@@ -3186,7 +3183,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="6" t="s">
         <v>26</v>
@@ -3202,7 +3199,7 @@
         <v>84</v>
       </c>
       <c r="G22" s="2"/>
-      <c r="H22" s="24" t="s">
+      <c r="H22" s="21" t="s">
         <v>7</v>
       </c>
       <c r="I22" s="7" t="s">
@@ -3216,7 +3213,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="8" t="s">
         <v>18</v>
@@ -3246,7 +3243,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="8" t="s">
         <v>31</v>
@@ -3272,7 +3269,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="8" t="s">
         <v>34</v>
@@ -3298,7 +3295,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="1"/>
@@ -3320,12 +3317,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="19"/>
+      <c r="C27" s="23"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="1"/>
@@ -3344,7 +3341,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="3" t="s">
         <v>4</v>
@@ -3370,7 +3367,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="8" t="s">
         <v>27</v>
@@ -3396,7 +3393,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="17" t="s">
         <v>35</v>
@@ -3408,7 +3405,7 @@
       <c r="E30" s="2"/>
       <c r="F30" s="1"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="25" t="s">
+      <c r="H30" s="22" t="s">
         <v>79</v>
       </c>
       <c r="I30" s="7" t="s">
@@ -3422,7 +3419,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="8" t="s">
         <v>79</v>
@@ -3440,7 +3437,7 @@
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="6" t="s">
         <v>22</v>
@@ -3451,23 +3448,23 @@
       <c r="E32" s="2"/>
       <c r="F32" s="1"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="20" t="s">
+      <c r="H32" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="21"/>
+      <c r="I32" s="25"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="19" t="s">
+      <c r="K32" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="19"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L32" s="23"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="6" t="s">
         <v>42</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="1"/>
@@ -3486,7 +3483,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="8" t="s">
         <v>41</v>
@@ -3511,7 +3508,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="13" t="s">
         <v>80</v>
@@ -3536,7 +3533,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="1"/>
@@ -3557,7 +3554,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="1"/>
@@ -3578,7 +3575,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="1"/>
@@ -3707,13 +3704,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09747FE2-332F-458B-9A08-92605154E49F}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="95.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="95.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="94.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="94.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>50</v>
       </c>
@@ -3721,7 +3718,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
         <v>10</v>
       </c>
@@ -3729,7 +3726,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>7</v>
       </c>
@@ -3737,7 +3734,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>17</v>
       </c>
@@ -3745,7 +3742,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>21</v>
       </c>
@@ -3753,7 +3750,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>22</v>
       </c>
@@ -3761,7 +3758,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>15</v>
       </c>
@@ -3769,7 +3766,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>58</v>
       </c>
@@ -3777,7 +3774,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>60</v>
       </c>
@@ -3785,7 +3782,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>20</v>
       </c>
@@ -3793,7 +3790,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>16</v>
       </c>
@@ -3801,7 +3798,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>63</v>
       </c>
@@ -3809,7 +3806,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>26</v>
       </c>
@@ -3817,7 +3814,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>66</v>
       </c>
@@ -3825,7 +3822,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>12</v>
       </c>
@@ -3833,7 +3830,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>41</v>
       </c>
@@ -3841,7 +3838,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>44</v>
       </c>
@@ -3849,7 +3846,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>30</v>
       </c>
@@ -3857,7 +3854,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>42</v>
       </c>
@@ -3865,7 +3862,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="145" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" ht="144" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>27</v>
       </c>
@@ -3873,7 +3870,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
         <v>34</v>
       </c>
@@ -3881,7 +3878,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>43</v>
       </c>
@@ -3889,7 +3886,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
         <v>49</v>
       </c>
@@ -3897,7 +3894,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>19</v>
       </c>
@@ -3905,7 +3902,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
         <v>36</v>
       </c>
@@ -3920,6 +3917,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -4120,22 +4132,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4152,21 +4166,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Septiembre.xlsx
+++ b/Cronograma de Tareas/Cronograma Septiembre.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/luis_fuentes_virtualsoft_tech/Documents/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{916904B6-0074-4A61-814B-CAA1D2DFFDAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F9974B-1081-44A4-BE8C-281FC6BCBC91}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-28920" yWindow="-870" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 31 Ago al 6 Sep" sheetId="8" r:id="rId1"/>
     <sheet name="Semana 2 - 7 Sep al 13 Sep" sheetId="9" r:id="rId2"/>
-    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId3"/>
+    <sheet name="Semana 3 - 14 al 20 Sep" sheetId="15" r:id="rId3"/>
+    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -28,9 +29,6 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -41,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="103">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -370,12 +368,42 @@
   <si>
     <t>Apoyo Revisión GGR negativo casino / deportivo</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Apoyo Revisión GGR negativo casino / deportivo// </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lunes y Martes hasta 1:00pm y Miercoles y Jueves hasta las 11:00am, en ausencia de Josue</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Apoyo Deltas (Registros, Bonos, Premios Bonos y Bonos Casino)// </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lunes y Martes hasta 1:00pm y Miercoles y Jueves hasta las 11:00am, en ausencia de Josue</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -419,8 +447,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -445,8 +501,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0D0D0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -521,11 +589,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -596,6 +684,45 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1604,24 +1731,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CAF266D-0085-4B50-B3FE-269B78B845C1}">
   <dimension ref="A2:L41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="15" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" customWidth="1"/>
-    <col min="2" max="2" width="56.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.5546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.3984375" customWidth="1"/>
+    <col min="2" max="2" width="56.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.3984375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.59765625" style="2" customWidth="1"/>
     <col min="8" max="8" width="55" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.44140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.3984375" style="2" customWidth="1"/>
     <col min="11" max="11" width="55" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.19921875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="15" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" s="2" customFormat="1">
       <c r="B2" s="23" t="s">
         <v>0</v>
       </c>
@@ -1640,7 +1767,7 @@
       </c>
       <c r="L2" s="23"/>
     </row>
-    <row r="3" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1667,7 +1794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1693,7 +1820,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -1719,7 +1846,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -1745,7 +1872,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -1771,7 +1898,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -1797,7 +1924,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -1823,7 +1950,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -1849,7 +1976,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B11" s="8" t="s">
         <v>30</v>
       </c>
@@ -1875,7 +2002,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B12" s="6" t="s">
         <v>36</v>
       </c>
@@ -1901,7 +2028,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B13" s="6" t="s">
         <v>12</v>
       </c>
@@ -1928,7 +2055,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B14" s="6" t="s">
         <v>85</v>
       </c>
@@ -1955,7 +2082,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="E15" s="6" t="s">
         <v>36</v>
       </c>
@@ -1975,7 +2102,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="F16"/>
       <c r="G16" s="1"/>
       <c r="H16" s="8" t="s">
@@ -1992,7 +2119,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" s="2" customFormat="1">
       <c r="B17" s="23" t="s">
         <v>25</v>
       </c>
@@ -2002,7 +2129,7 @@
       </c>
       <c r="F17" s="23"/>
     </row>
-    <row r="18" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B18" s="3" t="s">
         <v>4</v>
       </c>
@@ -2024,7 +2151,7 @@
       </c>
       <c r="L18" s="23"/>
     </row>
-    <row r="19" spans="2:12" s="2" customFormat="1" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" s="2" customFormat="1" ht="28.95" customHeight="1">
       <c r="B19" s="6" t="s">
         <v>12</v>
       </c>
@@ -2050,7 +2177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" s="2" customFormat="1">
       <c r="B20" s="6" t="s">
         <v>16</v>
       </c>
@@ -2076,7 +2203,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" s="2" customFormat="1">
       <c r="B21" s="6" t="s">
         <v>23</v>
       </c>
@@ -2102,7 +2229,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" s="2" customFormat="1">
       <c r="B22" s="6" t="s">
         <v>26</v>
       </c>
@@ -2128,7 +2255,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" s="2" customFormat="1">
       <c r="B23" s="8" t="s">
         <v>18</v>
       </c>
@@ -2149,7 +2276,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="2:12" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" s="2" customFormat="1" ht="27.6">
       <c r="B24" s="8" t="s">
         <v>31</v>
       </c>
@@ -2170,7 +2297,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" s="2" customFormat="1">
       <c r="B25" s="8" t="s">
         <v>34</v>
       </c>
@@ -2191,7 +2318,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" s="2" customFormat="1">
       <c r="C26" s="1"/>
       <c r="F26" s="1"/>
       <c r="H26" s="12" t="s">
@@ -2207,7 +2334,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" s="2" customFormat="1">
       <c r="B27" s="18" t="s">
         <v>38</v>
       </c>
@@ -2226,7 +2353,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B28" s="3" t="s">
         <v>4</v>
       </c>
@@ -2247,7 +2374,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" s="2" customFormat="1">
       <c r="B29" s="8" t="s">
         <v>27</v>
       </c>
@@ -2268,7 +2395,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" s="2" customFormat="1" ht="27.6">
       <c r="B30" s="17" t="s">
         <v>35</v>
       </c>
@@ -2290,7 +2417,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" s="2" customFormat="1">
       <c r="B31" s="8" t="s">
         <v>79</v>
       </c>
@@ -2299,7 +2426,7 @@
       </c>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" s="2" customFormat="1">
       <c r="B32" s="6" t="s">
         <v>22</v>
       </c>
@@ -2317,7 +2444,7 @@
       </c>
       <c r="L32" s="23"/>
     </row>
-    <row r="33" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B33" s="6" t="s">
         <v>42</v>
       </c>
@@ -2339,7 +2466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" s="2" customFormat="1">
       <c r="B34" s="6" t="s">
         <v>42</v>
       </c>
@@ -2361,7 +2488,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" s="2" customFormat="1">
       <c r="B35" s="8" t="s">
         <v>41</v>
       </c>
@@ -2383,7 +2510,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" s="2" customFormat="1">
       <c r="B36" s="13" t="s">
         <v>80</v>
       </c>
@@ -2405,7 +2532,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" s="2" customFormat="1">
       <c r="B37" s="6" t="s">
         <v>44</v>
       </c>
@@ -2427,7 +2554,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12" s="2" customFormat="1">
       <c r="C38" s="1"/>
       <c r="D38"/>
       <c r="F38" s="1"/>
@@ -2444,33 +2571,33 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12" s="2" customFormat="1">
       <c r="C39" s="1"/>
       <c r="D39"/>
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:12" s="2" customFormat="1">
       <c r="C40" s="1"/>
       <c r="D40"/>
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:12" s="2" customFormat="1">
       <c r="C41" s="1"/>
       <c r="D41"/>
       <c r="F41" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="H18:I18"/>
     <mergeCell ref="K18:L18"/>
     <mergeCell ref="H32:I32"/>
     <mergeCell ref="K32:L32"/>
     <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="66" priority="35"/>
@@ -2593,20 +2720,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4492F1BB-C491-4DF0-AED4-7076F62446D0}">
   <dimension ref="A1:L38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="2.44140625" customWidth="1"/>
-    <col min="2" max="2" width="87.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="47.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="49.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3984375" customWidth="1"/>
+    <col min="2" max="2" width="87.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="47.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="49.796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="1"/>
@@ -2620,7 +2747,7 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12">
       <c r="A2" s="2"/>
       <c r="B2" s="23" t="s">
         <v>0</v>
@@ -2642,7 +2769,7 @@
       </c>
       <c r="L2" s="23"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="14.4">
       <c r="A3" s="2"/>
       <c r="B3" s="3" t="s">
         <v>4</v>
@@ -2672,7 +2799,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="14.4">
       <c r="A4" s="2"/>
       <c r="B4" s="4" t="s">
         <v>7</v>
@@ -2702,7 +2829,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="14.4">
       <c r="A5" s="2"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -2732,7 +2859,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="14.4">
       <c r="A6" s="2"/>
       <c r="B6" s="6" t="s">
         <v>9</v>
@@ -2762,7 +2889,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="14.4">
       <c r="A7" s="2"/>
       <c r="B7" s="6" t="s">
         <v>15</v>
@@ -2792,7 +2919,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="14.4">
       <c r="A8" s="2"/>
       <c r="B8" s="6" t="s">
         <v>17</v>
@@ -2822,7 +2949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="14.4">
       <c r="A9" s="2"/>
       <c r="B9" s="6" t="s">
         <v>20</v>
@@ -2852,7 +2979,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="14.4">
       <c r="A10" s="2"/>
       <c r="B10" s="6" t="s">
         <v>21</v>
@@ -2882,7 +3009,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="14.4">
       <c r="A11" s="2"/>
       <c r="B11" s="8" t="s">
         <v>30</v>
@@ -2912,7 +3039,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="14.4">
       <c r="A12" s="2"/>
       <c r="B12" s="6" t="s">
         <v>36</v>
@@ -2942,7 +3069,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="14.4">
       <c r="A13" s="2"/>
       <c r="B13" s="6" t="s">
         <v>100</v>
@@ -2972,7 +3099,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="14.4">
       <c r="A14" s="2"/>
       <c r="B14" s="6" t="s">
         <v>85</v>
@@ -3002,7 +3129,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="14.4">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="1"/>
@@ -3028,7 +3155,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="14.4">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="1"/>
@@ -3054,7 +3181,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12">
       <c r="A17" s="2"/>
       <c r="B17" s="23" t="s">
         <v>25</v>
@@ -3069,7 +3196,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="14.4">
       <c r="A18" s="2"/>
       <c r="B18" s="3" t="s">
         <v>4</v>
@@ -3093,7 +3220,7 @@
       </c>
       <c r="L18" s="23"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="14.4">
       <c r="A19" s="2"/>
       <c r="B19" s="6" t="s">
         <v>12</v>
@@ -3123,7 +3250,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="14.4">
       <c r="A20" s="2"/>
       <c r="B20" s="6" t="s">
         <v>16</v>
@@ -3153,7 +3280,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12">
       <c r="A21" s="2"/>
       <c r="B21" s="6" t="s">
         <v>23</v>
@@ -3183,7 +3310,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="14.4">
       <c r="A22" s="2"/>
       <c r="B22" s="6" t="s">
         <v>26</v>
@@ -3213,7 +3340,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12">
       <c r="A23" s="2"/>
       <c r="B23" s="8" t="s">
         <v>18</v>
@@ -3243,7 +3370,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="27.6">
       <c r="A24" s="2"/>
       <c r="B24" s="8" t="s">
         <v>31</v>
@@ -3269,7 +3396,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12">
       <c r="A25" s="2"/>
       <c r="B25" s="8" t="s">
         <v>34</v>
@@ -3295,7 +3422,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="14.4">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="1"/>
@@ -3317,7 +3444,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12">
       <c r="A27" s="2"/>
       <c r="B27" s="23" t="s">
         <v>38</v>
@@ -3341,7 +3468,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="14.4">
       <c r="A28" s="2"/>
       <c r="B28" s="3" t="s">
         <v>4</v>
@@ -3367,7 +3494,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12">
       <c r="A29" s="2"/>
       <c r="B29" s="8" t="s">
         <v>27</v>
@@ -3393,7 +3520,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="14.4">
       <c r="A30" s="2"/>
       <c r="B30" s="17" t="s">
         <v>35</v>
@@ -3419,7 +3546,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12">
       <c r="A31" s="2"/>
       <c r="B31" s="8" t="s">
         <v>79</v>
@@ -3437,7 +3564,7 @@
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12">
       <c r="A32" s="2"/>
       <c r="B32" s="6" t="s">
         <v>22</v>
@@ -3458,7 +3585,7 @@
       </c>
       <c r="L32" s="23"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="14.4">
       <c r="A33" s="2"/>
       <c r="B33" s="6" t="s">
         <v>42</v>
@@ -3483,7 +3610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12">
       <c r="A34" s="2"/>
       <c r="B34" s="8" t="s">
         <v>41</v>
@@ -3508,7 +3635,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12">
       <c r="A35" s="2"/>
       <c r="B35" s="13" t="s">
         <v>80</v>
@@ -3533,7 +3660,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="1"/>
@@ -3554,7 +3681,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="1"/>
@@ -3575,7 +3702,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="1"/>
@@ -3702,15 +3829,1137 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A660AB6E-2BEB-478D-AB14-1796ACC95819}">
+  <dimension ref="A1:L41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="2.8984375" customWidth="1"/>
+    <col min="2" max="2" width="49.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.59765625" customWidth="1"/>
+    <col min="5" max="5" width="49.8984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.59765625" customWidth="1"/>
+    <col min="8" max="8" width="49.8984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.3984375" customWidth="1"/>
+    <col min="11" max="11" width="52" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.59765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="34"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="26"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="26"/>
+      <c r="B2" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="36"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="36"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="36"/>
+    </row>
+    <row r="3" spans="1:12" ht="14.4">
+      <c r="A3" s="26"/>
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="27"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="26"/>
+      <c r="H3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="26"/>
+      <c r="K3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.4">
+      <c r="A4" s="26"/>
+      <c r="B4" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="26"/>
+      <c r="E4" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="26"/>
+      <c r="H4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" s="26"/>
+      <c r="K4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="14.4">
+      <c r="A5" s="26"/>
+      <c r="B5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="26"/>
+      <c r="E5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="26"/>
+      <c r="H5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="26"/>
+      <c r="K5" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="L5" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.4">
+      <c r="A6" s="26"/>
+      <c r="B6" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="26"/>
+      <c r="E6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="26"/>
+      <c r="H6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="26"/>
+      <c r="K6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.4">
+      <c r="A7" s="26"/>
+      <c r="B7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="26"/>
+      <c r="E7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="26"/>
+      <c r="H7" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="26"/>
+      <c r="K7" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="L7" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="14.4">
+      <c r="A8" s="26"/>
+      <c r="B8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="26"/>
+      <c r="E8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="26"/>
+      <c r="H8" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="26"/>
+      <c r="K8" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="14.4">
+      <c r="A9" s="26"/>
+      <c r="B9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="26"/>
+      <c r="E9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="26"/>
+      <c r="H9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="26"/>
+      <c r="K9" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="14.4">
+      <c r="A10" s="26"/>
+      <c r="B10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="26"/>
+      <c r="E10" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="26"/>
+      <c r="H10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" s="26"/>
+      <c r="K10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="14.4">
+      <c r="A11" s="26"/>
+      <c r="B11" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="26"/>
+      <c r="E11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="26"/>
+      <c r="H11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="26"/>
+      <c r="K11" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="L11" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="14.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="26"/>
+      <c r="H12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="26"/>
+      <c r="K12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="41.4">
+      <c r="A13" s="26"/>
+      <c r="B13" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="27"/>
+      <c r="E13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="26"/>
+      <c r="H13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="26"/>
+      <c r="K13" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="L13" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="41.4">
+      <c r="A14" s="26"/>
+      <c r="B14" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="26"/>
+      <c r="H14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="26"/>
+      <c r="K14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.4">
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="26"/>
+      <c r="H15" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="26"/>
+      <c r="K15" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="L15" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.4">
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" s="27"/>
+      <c r="K16" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="L16" s="29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="26"/>
+      <c r="B17" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="36"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" s="36"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="26"/>
+    </row>
+    <row r="18" spans="1:12" ht="14.4">
+      <c r="A18" s="26"/>
+      <c r="B18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="26"/>
+      <c r="E18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="26"/>
+      <c r="H18" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="36"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="L18" s="36"/>
+    </row>
+    <row r="19" spans="1:12" ht="14.4">
+      <c r="A19" s="26"/>
+      <c r="B19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="26"/>
+      <c r="E19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="26"/>
+      <c r="H19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J19" s="26"/>
+      <c r="K19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="14.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="26"/>
+      <c r="E20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="26"/>
+      <c r="H20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="26"/>
+      <c r="K20" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="L20" s="28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="26"/>
+      <c r="B21" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="26"/>
+      <c r="E21" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="26"/>
+      <c r="H21" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="J21" s="26"/>
+      <c r="K21" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" s="28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="14.4">
+      <c r="A22" s="26"/>
+      <c r="B22" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="26"/>
+      <c r="E22" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="26"/>
+      <c r="H22" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I22" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="J22" s="26"/>
+      <c r="K22" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="L22" s="28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="26"/>
+      <c r="B23" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="37"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I23" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" s="26"/>
+      <c r="K23" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="L23" s="28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="41.4">
+      <c r="A24" s="26"/>
+      <c r="B24" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="37"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="J24" s="26"/>
+      <c r="K24" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" s="28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="26"/>
+      <c r="B25" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="37"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" s="26"/>
+      <c r="K25" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="L25" s="28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="14.4">
+      <c r="A26" s="34"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="J26" s="26"/>
+      <c r="K26" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="L26" s="28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="26"/>
+      <c r="B27" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="36"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" s="26"/>
+      <c r="K27" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" s="28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="14.4">
+      <c r="A28" s="26"/>
+      <c r="B28" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="37"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="J28" s="26"/>
+      <c r="K28" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" s="28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="26"/>
+      <c r="B29" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="37"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="J29" s="26"/>
+      <c r="K29" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="L29" s="28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="27.6">
+      <c r="A30" s="26"/>
+      <c r="B30" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="37"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="I30" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="J30" s="27"/>
+      <c r="K30" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="L30" s="28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="26"/>
+      <c r="B31" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="37"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="34"/>
+      <c r="K31" s="34"/>
+      <c r="L31" s="26"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="26"/>
+      <c r="B32" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="39"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="I32" s="40"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="L32" s="36"/>
+    </row>
+    <row r="33" spans="1:12" ht="14.4">
+      <c r="A33" s="26"/>
+      <c r="B33" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="39"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="26"/>
+      <c r="K33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="26"/>
+      <c r="B34" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="39"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I34" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J34" s="26"/>
+      <c r="K34" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L34" s="28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="26"/>
+      <c r="B35" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="39"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J35" s="26"/>
+      <c r="K35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L35" s="28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="26"/>
+      <c r="B36" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="39"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I36" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J36" s="26"/>
+      <c r="K36" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="L36" s="28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="26"/>
+      <c r="B37" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" s="39"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J37" s="26"/>
+      <c r="K37" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L37" s="28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="34"/>
+      <c r="B38" s="34"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J38" s="26"/>
+      <c r="K38" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" s="28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="34"/>
+      <c r="B39" s="34"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="34"/>
+      <c r="K39" s="34"/>
+      <c r="L39" s="26"/>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="34"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="34"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="34"/>
+      <c r="K40" s="34"/>
+      <c r="L40" s="26"/>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="34"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="34"/>
+      <c r="K41" s="34"/>
+      <c r="L41" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="52">
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09747FE2-332F-458B-9A08-92605154E49F}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="95.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="95.19921875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="47.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="94.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="94.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="14" t="s">
         <v>50</v>
       </c>
@@ -3718,7 +4967,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="27.6">
       <c r="A2" s="15" t="s">
         <v>10</v>
       </c>
@@ -3726,7 +4975,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="27.6">
       <c r="A3" s="15" t="s">
         <v>7</v>
       </c>
@@ -3734,7 +4983,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="27.6">
       <c r="A4" s="15" t="s">
         <v>17</v>
       </c>
@@ -3742,7 +4991,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="27.6">
       <c r="A5" s="15" t="s">
         <v>21</v>
       </c>
@@ -3750,7 +4999,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="41.4">
       <c r="A6" s="15" t="s">
         <v>22</v>
       </c>
@@ -3758,7 +5007,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="14.4">
       <c r="A7" s="15" t="s">
         <v>15</v>
       </c>
@@ -3766,7 +5015,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="55.2">
       <c r="A8" s="15" t="s">
         <v>58</v>
       </c>
@@ -3774,7 +5023,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="27.6">
       <c r="A9" s="15" t="s">
         <v>60</v>
       </c>
@@ -3782,7 +5031,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="14.4">
       <c r="A10" s="15" t="s">
         <v>20</v>
       </c>
@@ -3790,7 +5039,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="41.4">
       <c r="A11" s="15" t="s">
         <v>16</v>
       </c>
@@ -3798,7 +5047,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="41.4">
       <c r="A12" s="15" t="s">
         <v>63</v>
       </c>
@@ -3806,7 +5055,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="41.4">
       <c r="A13" s="15" t="s">
         <v>26</v>
       </c>
@@ -3814,7 +5063,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="27.6">
       <c r="A14" s="15" t="s">
         <v>66</v>
       </c>
@@ -3822,7 +5071,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="96.6">
       <c r="A15" s="15" t="s">
         <v>12</v>
       </c>
@@ -3830,7 +5079,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="96.6">
       <c r="A16" s="15" t="s">
         <v>41</v>
       </c>
@@ -3838,7 +5087,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="41.4">
       <c r="A17" s="15" t="s">
         <v>44</v>
       </c>
@@ -3846,7 +5095,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="27.6">
       <c r="A18" s="15" t="s">
         <v>30</v>
       </c>
@@ -3854,7 +5103,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="27.6">
       <c r="A19" s="15" t="s">
         <v>42</v>
       </c>
@@ -3862,7 +5111,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="144" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="138">
       <c r="A20" s="15" t="s">
         <v>27</v>
       </c>
@@ -3870,7 +5119,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="55.2">
       <c r="A21" s="15" t="s">
         <v>34</v>
       </c>
@@ -3878,7 +5127,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="41.4">
       <c r="A22" s="16" t="s">
         <v>43</v>
       </c>
@@ -3886,7 +5135,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="96.6">
       <c r="A23" s="15" t="s">
         <v>49</v>
       </c>
@@ -3894,7 +5143,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="55.2">
       <c r="A24" s="15" t="s">
         <v>19</v>
       </c>
@@ -3902,7 +5151,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="41.4">
       <c r="A25" s="15" t="s">
         <v>36</v>
       </c>
@@ -3917,21 +5166,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -4132,24 +5366,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4166,4 +5398,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>